--- a/testdata/jobtitle.xlsx
+++ b/testdata/jobtitle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Techifynow\LearnPlaywrightTechifynowB3\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B277D7-9A72-4A97-A652-6F953B8DC197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DDAC4BA-9294-40AE-B970-77044226FDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{10DA23AA-7ABB-4CC2-A4C8-FCF4F50A8575}"/>
   </bookViews>
@@ -41,13 +41,13 @@
     <t>jobtitle</t>
   </si>
   <si>
-    <t>SDET123</t>
-  </si>
-  <si>
     <t>jobdescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Automation Scriptting </t>
+    <t xml:space="preserve">RajuTitle </t>
+  </si>
+  <si>
+    <t>Automation Scriptting  1234</t>
   </si>
 </sst>
 </file>
@@ -421,18 +421,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E28EE9A-E9E7-4F78-8961-085DA4F8BBD7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
